--- a/data/climate_data/indicateurs_journaliers_par_essais/1.1.4.2.5_R2015/191022_SYN15_IPC_Calcul_ok.xlsx
+++ b/data/climate_data/indicateurs_journaliers_par_essais/1.1.4.2.5_R2015/191022_SYN15_IPC_Calcul_ok.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="61">
   <si>
     <t xml:space="preserve">TEMPERATURE</t>
   </si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t xml:space="preserve">Fin FLO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">a</t>
   </si>
   <si>
     <t xml:space="preserve">PRELIQ_Q (mm)</t>
@@ -1093,7 +1096,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AD316"/>
+  <dimension ref="A1:AD317"/>
   <sheetFormatPr defaultColWidth="10.54296875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25226,6 +25229,41 @@
       </c>
       <c r="AA316" s="8" t="n">
         <v>16.100002490156</v>
+      </c>
+    </row>
+    <row r="317" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A317" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="B317" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="C317" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="D317" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="E317" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="F317" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="G317" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="H317" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="I317" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="J317" s="0" t="s">
+        <v>57</v>
+      </c>
+      <c r="K317" s="0" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -25398,7 +25436,7 @@
         <v>10</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>12</v>
@@ -25413,7 +25451,7 @@
         <v>15</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="P4" s="1" t="s">
         <v>17</v>
@@ -38970,7 +39008,7 @@
         <v>11.0452205681135</v>
       </c>
       <c r="AB188" s="33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="189" s="8" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
